--- a/docs/qa/upload-templates/quality_results_upload_template.xlsx
+++ b/docs/qa/upload-templates/quality_results_upload_template.xlsx
@@ -131,17 +131,17 @@
     <author>IPE</author>
   </authors>
   <commentList>
-    <comment ref="B1" authorId="0" shapeId="0">
+    <comment ref="C1" authorId="0" shapeId="0">
       <text>
         <t>YYYY-MM-DD</t>
       </text>
     </comment>
-    <comment ref="C1" authorId="0" shapeId="0">
+    <comment ref="D1" authorId="0" shapeId="0">
       <text>
         <t>pass|fail|on_hold</t>
       </text>
     </comment>
-    <comment ref="D1" authorId="0" shapeId="0">
+    <comment ref="E1" authorId="0" shapeId="0">
       <text>
         <t>Numeric</t>
       </text>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -450,22 +450,37 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>product_code</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>inspection_date</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>result</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>measured_value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>defect_type</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>inspector</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
@@ -477,20 +492,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>FG-DT100</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>fail</t>
         </is>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>0.15</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>winding_tension</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>QC-01</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Rework winding</t>
         </is>
       </c>
     </row>
@@ -502,18 +532,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>FG-DT250</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>0.98</v>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>QC-02</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -523,18 +564,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>FG-DT100</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>pass</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>0.99</v>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>QC-01</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
